--- a/ERDEMLİ.xlsx
+++ b/ERDEMLİ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J730"/>
+  <dimension ref="A1:K730"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,6 +431,9 @@
       <c r="J1" t="str">
         <v>Tescil Önceliği</v>
       </c>
+      <c r="K1" t="str">
+        <v>İşlem Tarihi</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -487,14 +490,17 @@
         <v>Yol</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>DOPTAN İHDAS belirtilecek.</v>
       </c>
       <c r="J3" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K3" t="str">
+        <v>2026-04-07</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -23762,7 +23768,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J730"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K730"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ERDEMLİ.xlsx
+++ b/ERDEMLİ.xlsx
@@ -493,7 +493,7 @@
         <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I3" t="str">
-        <v>DOPTAN İHDAS belirtilecek.</v>
+        <v>Nitelik ARSA- DOPTAN İHDAS belirtilecek.</v>
       </c>
       <c r="J3" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>

--- a/ERDEMLİ.xlsx
+++ b/ERDEMLİ.xlsx
@@ -466,6 +466,9 @@
       <c r="J2" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -533,6 +536,9 @@
       <c r="J4" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -565,6 +571,9 @@
       <c r="J5" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -597,6 +606,9 @@
       <c r="J6" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -629,6 +641,9 @@
       <c r="J7" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -661,6 +676,9 @@
       <c r="J8" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -693,6 +711,9 @@
       <c r="J9" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -725,6 +746,9 @@
       <c r="J10" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -757,6 +781,9 @@
       <c r="J11" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -789,6 +816,9 @@
       <c r="J12" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -821,6 +851,9 @@
       <c r="J13" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -853,6 +886,9 @@
       <c r="J14" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -885,6 +921,9 @@
       <c r="J15" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -917,6 +956,9 @@
       <c r="J16" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -949,6 +991,9 @@
       <c r="J17" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -981,6 +1026,9 @@
       <c r="J18" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1013,6 +1061,9 @@
       <c r="J19" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1045,6 +1096,9 @@
       <c r="J20" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1077,6 +1131,9 @@
       <c r="J21" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1109,6 +1166,9 @@
       <c r="J22" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1141,6 +1201,9 @@
       <c r="J23" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1173,6 +1236,9 @@
       <c r="J24" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1205,6 +1271,9 @@
       <c r="J25" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1237,6 +1306,9 @@
       <c r="J26" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1269,6 +1341,9 @@
       <c r="J27" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1301,6 +1376,9 @@
       <c r="J28" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1333,6 +1411,9 @@
       <c r="J29" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1365,6 +1446,9 @@
       <c r="J30" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1397,6 +1481,9 @@
       <c r="J31" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1429,6 +1516,9 @@
       <c r="J32" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1461,6 +1551,9 @@
       <c r="J33" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1493,6 +1586,9 @@
       <c r="J34" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1525,6 +1621,9 @@
       <c r="J35" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1557,6 +1656,9 @@
       <c r="J36" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1589,6 +1691,9 @@
       <c r="J37" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1621,6 +1726,9 @@
       <c r="J38" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1653,6 +1761,9 @@
       <c r="J39" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1685,6 +1796,9 @@
       <c r="J40" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1717,6 +1831,9 @@
       <c r="J41" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1749,6 +1866,9 @@
       <c r="J42" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1781,6 +1901,9 @@
       <c r="J43" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1813,6 +1936,9 @@
       <c r="J44" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1845,6 +1971,9 @@
       <c r="J45" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1877,6 +2006,9 @@
       <c r="J46" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1909,6 +2041,9 @@
       <c r="J47" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1941,6 +2076,9 @@
       <c r="J48" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1973,6 +2111,9 @@
       <c r="J49" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2005,6 +2146,9 @@
       <c r="J50" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2037,6 +2181,9 @@
       <c r="J51" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2069,6 +2216,9 @@
       <c r="J52" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2101,6 +2251,9 @@
       <c r="J53" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2133,6 +2286,9 @@
       <c r="J54" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2165,6 +2321,9 @@
       <c r="J55" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2197,6 +2356,9 @@
       <c r="J56" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2229,6 +2391,9 @@
       <c r="J57" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2261,6 +2426,9 @@
       <c r="J58" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2293,6 +2461,9 @@
       <c r="J59" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2325,6 +2496,9 @@
       <c r="J60" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2357,6 +2531,9 @@
       <c r="J61" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2389,6 +2566,9 @@
       <c r="J62" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2421,6 +2601,9 @@
       <c r="J63" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2453,6 +2636,9 @@
       <c r="J64" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2485,6 +2671,9 @@
       <c r="J65" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2517,6 +2706,9 @@
       <c r="J66" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -2549,6 +2741,9 @@
       <c r="J67" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -2581,6 +2776,9 @@
       <c r="J68" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -2613,6 +2811,9 @@
       <c r="J69" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -2645,6 +2846,9 @@
       <c r="J70" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -2677,6 +2881,9 @@
       <c r="J71" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -2709,6 +2916,9 @@
       <c r="J72" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -2741,6 +2951,9 @@
       <c r="J73" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -2773,6 +2986,9 @@
       <c r="J74" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -2805,6 +3021,9 @@
       <c r="J75" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -2837,6 +3056,9 @@
       <c r="J76" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -2869,6 +3091,9 @@
       <c r="J77" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -2901,6 +3126,9 @@
       <c r="J78" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -2933,6 +3161,9 @@
       <c r="J79" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -2965,6 +3196,9 @@
       <c r="J80" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -2997,6 +3231,9 @@
       <c r="J81" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -3029,6 +3266,9 @@
       <c r="J82" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -3061,6 +3301,9 @@
       <c r="J83" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -3093,6 +3336,9 @@
       <c r="J84" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -3125,6 +3371,9 @@
       <c r="J85" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -3157,6 +3406,9 @@
       <c r="J86" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -3189,6 +3441,9 @@
       <c r="J87" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -3221,6 +3476,9 @@
       <c r="J88" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -3253,6 +3511,9 @@
       <c r="J89" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -3285,6 +3546,9 @@
       <c r="J90" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -3317,6 +3581,9 @@
       <c r="J91" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -3349,6 +3616,9 @@
       <c r="J92" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -3381,6 +3651,9 @@
       <c r="J93" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -3413,6 +3686,9 @@
       <c r="J94" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -3445,6 +3721,9 @@
       <c r="J95" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -3477,6 +3756,9 @@
       <c r="J96" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -3509,6 +3791,9 @@
       <c r="J97" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -3541,6 +3826,9 @@
       <c r="J98" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -3573,6 +3861,9 @@
       <c r="J99" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -3605,6 +3896,9 @@
       <c r="J100" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -3637,6 +3931,9 @@
       <c r="J101" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -3669,6 +3966,9 @@
       <c r="J102" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -3701,6 +4001,9 @@
       <c r="J103" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -3733,6 +4036,9 @@
       <c r="J104" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -3765,6 +4071,9 @@
       <c r="J105" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -3797,6 +4106,9 @@
       <c r="J106" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -3829,6 +4141,9 @@
       <c r="J107" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -3861,6 +4176,9 @@
       <c r="J108" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -3893,6 +4211,9 @@
       <c r="J109" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -3925,6 +4246,9 @@
       <c r="J110" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -3957,6 +4281,9 @@
       <c r="J111" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -3989,6 +4316,9 @@
       <c r="J112" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -4021,6 +4351,9 @@
       <c r="J113" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4053,6 +4386,9 @@
       <c r="J114" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -4085,6 +4421,9 @@
       <c r="J115" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -4117,6 +4456,9 @@
       <c r="J116" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -4149,6 +4491,9 @@
       <c r="J117" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -4181,6 +4526,9 @@
       <c r="J118" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -4213,6 +4561,9 @@
       <c r="J119" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -4245,6 +4596,9 @@
       <c r="J120" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -4277,6 +4631,9 @@
       <c r="J121" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -4309,6 +4666,9 @@
       <c r="J122" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -4341,6 +4701,9 @@
       <c r="J123" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -4373,6 +4736,9 @@
       <c r="J124" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -4405,6 +4771,9 @@
       <c r="J125" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -4437,6 +4806,9 @@
       <c r="J126" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -4469,6 +4841,9 @@
       <c r="J127" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -4501,6 +4876,9 @@
       <c r="J128" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -4533,6 +4911,9 @@
       <c r="J129" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -4565,6 +4946,9 @@
       <c r="J130" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -4597,6 +4981,9 @@
       <c r="J131" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -4629,6 +5016,9 @@
       <c r="J132" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -4661,6 +5051,9 @@
       <c r="J133" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -4693,6 +5086,9 @@
       <c r="J134" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -4725,6 +5121,9 @@
       <c r="J135" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -4757,6 +5156,9 @@
       <c r="J136" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -4789,6 +5191,9 @@
       <c r="J137" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -4821,6 +5226,9 @@
       <c r="J138" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -4853,6 +5261,9 @@
       <c r="J139" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -4885,6 +5296,9 @@
       <c r="J140" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -4917,6 +5331,9 @@
       <c r="J141" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -4949,6 +5366,9 @@
       <c r="J142" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -4981,6 +5401,9 @@
       <c r="J143" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -5013,6 +5436,9 @@
       <c r="J144" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -5045,6 +5471,9 @@
       <c r="J145" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -5077,6 +5506,9 @@
       <c r="J146" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -5109,6 +5541,9 @@
       <c r="J147" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -5141,6 +5576,9 @@
       <c r="J148" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -5173,6 +5611,9 @@
       <c r="J149" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -5205,6 +5646,9 @@
       <c r="J150" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -5237,6 +5681,9 @@
       <c r="J151" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -5269,6 +5716,9 @@
       <c r="J152" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -5301,6 +5751,9 @@
       <c r="J153" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -5333,6 +5786,9 @@
       <c r="J154" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -5365,6 +5821,9 @@
       <c r="J155" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -5397,6 +5856,9 @@
       <c r="J156" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -5429,6 +5891,9 @@
       <c r="J157" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -5461,6 +5926,9 @@
       <c r="J158" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -5493,6 +5961,9 @@
       <c r="J159" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -5525,6 +5996,9 @@
       <c r="J160" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -5557,6 +6031,9 @@
       <c r="J161" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -5589,6 +6066,9 @@
       <c r="J162" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -5621,6 +6101,9 @@
       <c r="J163" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -5653,6 +6136,9 @@
       <c r="J164" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -5685,6 +6171,9 @@
       <c r="J165" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -5717,6 +6206,9 @@
       <c r="J166" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -5749,6 +6241,9 @@
       <c r="J167" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -5781,6 +6276,9 @@
       <c r="J168" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -5813,6 +6311,9 @@
       <c r="J169" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -5845,6 +6346,9 @@
       <c r="J170" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -5877,6 +6381,9 @@
       <c r="J171" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -5909,6 +6416,9 @@
       <c r="J172" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -5941,6 +6451,9 @@
       <c r="J173" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -5973,6 +6486,9 @@
       <c r="J174" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -6005,6 +6521,9 @@
       <c r="J175" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -6037,6 +6556,9 @@
       <c r="J176" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -6069,6 +6591,9 @@
       <c r="J177" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -6101,6 +6626,9 @@
       <c r="J178" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -6133,6 +6661,9 @@
       <c r="J179" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -6165,6 +6696,9 @@
       <c r="J180" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -6197,6 +6731,9 @@
       <c r="J181" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -6229,6 +6766,9 @@
       <c r="J182" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -6261,6 +6801,9 @@
       <c r="J183" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -6293,6 +6836,9 @@
       <c r="J184" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -6325,6 +6871,9 @@
       <c r="J185" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -6357,6 +6906,9 @@
       <c r="J186" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -6389,6 +6941,9 @@
       <c r="J187" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -6421,6 +6976,9 @@
       <c r="J188" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -6453,6 +7011,9 @@
       <c r="J189" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -6485,6 +7046,9 @@
       <c r="J190" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -6517,6 +7081,9 @@
       <c r="J191" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -6549,6 +7116,9 @@
       <c r="J192" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -6581,6 +7151,9 @@
       <c r="J193" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -6613,6 +7186,9 @@
       <c r="J194" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -6645,6 +7221,9 @@
       <c r="J195" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -6677,6 +7256,9 @@
       <c r="J196" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -6709,6 +7291,9 @@
       <c r="J197" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -6741,6 +7326,9 @@
       <c r="J198" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -6773,6 +7361,9 @@
       <c r="J199" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -6805,6 +7396,9 @@
       <c r="J200" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -6837,6 +7431,9 @@
       <c r="J201" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -6869,6 +7466,9 @@
       <c r="J202" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -6901,6 +7501,9 @@
       <c r="J203" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -6933,6 +7536,9 @@
       <c r="J204" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -6965,6 +7571,9 @@
       <c r="J205" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -6997,6 +7606,9 @@
       <c r="J206" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -7029,6 +7641,9 @@
       <c r="J207" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -7061,6 +7676,9 @@
       <c r="J208" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -7093,6 +7711,9 @@
       <c r="J209" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -7125,6 +7746,9 @@
       <c r="J210" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -7157,6 +7781,9 @@
       <c r="J211" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -7189,6 +7816,9 @@
       <c r="J212" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -7221,6 +7851,9 @@
       <c r="J213" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -7253,6 +7886,9 @@
       <c r="J214" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -7285,6 +7921,9 @@
       <c r="J215" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -7317,6 +7956,9 @@
       <c r="J216" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -7349,6 +7991,9 @@
       <c r="J217" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -7381,6 +8026,9 @@
       <c r="J218" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -7413,6 +8061,9 @@
       <c r="J219" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -7445,6 +8096,9 @@
       <c r="J220" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -7477,6 +8131,9 @@
       <c r="J221" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -7509,6 +8166,9 @@
       <c r="J222" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -7541,6 +8201,9 @@
       <c r="J223" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -7573,6 +8236,9 @@
       <c r="J224" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -7605,6 +8271,9 @@
       <c r="J225" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -7637,6 +8306,9 @@
       <c r="J226" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -7669,6 +8341,9 @@
       <c r="J227" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -7701,6 +8376,9 @@
       <c r="J228" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -7733,6 +8411,9 @@
       <c r="J229" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -7765,6 +8446,9 @@
       <c r="J230" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -7797,6 +8481,9 @@
       <c r="J231" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -7829,6 +8516,9 @@
       <c r="J232" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -7861,6 +8551,9 @@
       <c r="J233" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -7893,6 +8586,9 @@
       <c r="J234" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -7925,6 +8621,9 @@
       <c r="J235" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -7957,6 +8656,9 @@
       <c r="J236" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -7989,6 +8691,9 @@
       <c r="J237" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -8021,6 +8726,9 @@
       <c r="J238" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -8053,6 +8761,9 @@
       <c r="J239" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -8085,6 +8796,9 @@
       <c r="J240" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -8117,6 +8831,9 @@
       <c r="J241" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -8149,6 +8866,9 @@
       <c r="J242" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -8181,6 +8901,9 @@
       <c r="J243" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -8213,6 +8936,9 @@
       <c r="J244" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -8245,6 +8971,9 @@
       <c r="J245" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -8277,6 +9006,9 @@
       <c r="J246" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -8309,6 +9041,9 @@
       <c r="J247" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -8341,6 +9076,9 @@
       <c r="J248" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -8373,6 +9111,9 @@
       <c r="J249" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -8405,6 +9146,9 @@
       <c r="J250" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -8437,6 +9181,9 @@
       <c r="J251" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -8469,6 +9216,9 @@
       <c r="J252" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -8501,6 +9251,9 @@
       <c r="J253" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -8533,6 +9286,9 @@
       <c r="J254" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -8565,6 +9321,9 @@
       <c r="J255" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -8597,6 +9356,9 @@
       <c r="J256" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -8629,6 +9391,9 @@
       <c r="J257" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -8661,6 +9426,9 @@
       <c r="J258" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -8693,6 +9461,9 @@
       <c r="J259" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K259" t="str">
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -8725,6 +9496,9 @@
       <c r="J260" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K260" t="str">
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -8757,6 +9531,9 @@
       <c r="J261" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K261" t="str">
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -8789,6 +9566,9 @@
       <c r="J262" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K262" t="str">
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -8821,6 +9601,9 @@
       <c r="J263" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K263" t="str">
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -8853,6 +9636,9 @@
       <c r="J264" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K264" t="str">
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -8885,6 +9671,9 @@
       <c r="J265" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K265" t="str">
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -8917,6 +9706,9 @@
       <c r="J266" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K266" t="str">
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -8949,6 +9741,9 @@
       <c r="J267" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K267" t="str">
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -8981,6 +9776,9 @@
       <c r="J268" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K268" t="str">
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -9013,6 +9811,9 @@
       <c r="J269" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K269" t="str">
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -9045,6 +9846,9 @@
       <c r="J270" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K270" t="str">
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -9077,6 +9881,9 @@
       <c r="J271" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K271" t="str">
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -9109,6 +9916,9 @@
       <c r="J272" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K272" t="str">
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -9141,6 +9951,9 @@
       <c r="J273" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K273" t="str">
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -9173,6 +9986,9 @@
       <c r="J274" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K274" t="str">
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -9205,6 +10021,9 @@
       <c r="J275" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K275" t="str">
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -9237,6 +10056,9 @@
       <c r="J276" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K276" t="str">
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -9269,6 +10091,9 @@
       <c r="J277" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K277" t="str">
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -9301,6 +10126,9 @@
       <c r="J278" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K278" t="str">
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -9333,6 +10161,9 @@
       <c r="J279" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K279" t="str">
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -9365,6 +10196,9 @@
       <c r="J280" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K280" t="str">
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -9397,6 +10231,9 @@
       <c r="J281" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K281" t="str">
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -9429,6 +10266,9 @@
       <c r="J282" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K282" t="str">
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -9461,6 +10301,9 @@
       <c r="J283" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K283" t="str">
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -9493,6 +10336,9 @@
       <c r="J284" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K284" t="str">
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -9525,6 +10371,9 @@
       <c r="J285" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K285" t="str">
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -9557,6 +10406,9 @@
       <c r="J286" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K286" t="str">
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -9589,6 +10441,9 @@
       <c r="J287" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K287" t="str">
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -9621,6 +10476,9 @@
       <c r="J288" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K288" t="str">
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -9653,6 +10511,9 @@
       <c r="J289" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K289" t="str">
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -9685,6 +10546,9 @@
       <c r="J290" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K290" t="str">
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -9717,6 +10581,9 @@
       <c r="J291" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K291" t="str">
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -9749,6 +10616,9 @@
       <c r="J292" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K292" t="str">
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -9781,6 +10651,9 @@
       <c r="J293" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K293" t="str">
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -9813,6 +10686,9 @@
       <c r="J294" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K294" t="str">
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -9845,6 +10721,9 @@
       <c r="J295" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K295" t="str">
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -9877,6 +10756,9 @@
       <c r="J296" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K296" t="str">
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -9909,6 +10791,9 @@
       <c r="J297" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K297" t="str">
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -9941,6 +10826,9 @@
       <c r="J298" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K298" t="str">
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -9973,6 +10861,9 @@
       <c r="J299" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K299" t="str">
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -10005,6 +10896,9 @@
       <c r="J300" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K300" t="str">
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -10037,6 +10931,9 @@
       <c r="J301" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K301" t="str">
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -10069,6 +10966,9 @@
       <c r="J302" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K302" t="str">
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -10101,6 +11001,9 @@
       <c r="J303" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K303" t="str">
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -10133,6 +11036,9 @@
       <c r="J304" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K304" t="str">
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -10165,6 +11071,9 @@
       <c r="J305" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K305" t="str">
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -10197,6 +11106,9 @@
       <c r="J306" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K306" t="str">
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -10229,6 +11141,9 @@
       <c r="J307" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K307" t="str">
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -10261,6 +11176,9 @@
       <c r="J308" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K308" t="str">
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -10293,6 +11211,9 @@
       <c r="J309" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K309" t="str">
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -10325,6 +11246,9 @@
       <c r="J310" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K310" t="str">
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -10357,6 +11281,9 @@
       <c r="J311" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K311" t="str">
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -10389,6 +11316,9 @@
       <c r="J312" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K312" t="str">
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -10421,6 +11351,9 @@
       <c r="J313" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K313" t="str">
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -10453,6 +11386,9 @@
       <c r="J314" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K314" t="str">
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -10485,6 +11421,9 @@
       <c r="J315" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K315" t="str">
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -10517,6 +11456,9 @@
       <c r="J316" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K316" t="str">
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -10549,6 +11491,9 @@
       <c r="J317" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K317" t="str">
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -10581,6 +11526,9 @@
       <c r="J318" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K318" t="str">
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -10613,6 +11561,9 @@
       <c r="J319" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K319" t="str">
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -10645,6 +11596,9 @@
       <c r="J320" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K320" t="str">
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -10677,6 +11631,9 @@
       <c r="J321" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K321" t="str">
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -10709,6 +11666,9 @@
       <c r="J322" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K322" t="str">
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -10741,6 +11701,9 @@
       <c r="J323" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K323" t="str">
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -10773,6 +11736,9 @@
       <c r="J324" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K324" t="str">
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -10805,6 +11771,9 @@
       <c r="J325" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K325" t="str">
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -10837,6 +11806,9 @@
       <c r="J326" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K326" t="str">
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -10869,6 +11841,9 @@
       <c r="J327" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K327" t="str">
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -10901,6 +11876,9 @@
       <c r="J328" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K328" t="str">
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -10933,6 +11911,9 @@
       <c r="J329" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K329" t="str">
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -10965,6 +11946,9 @@
       <c r="J330" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K330" t="str">
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -10997,6 +11981,9 @@
       <c r="J331" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K331" t="str">
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -11029,6 +12016,9 @@
       <c r="J332" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K332" t="str">
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -11061,6 +12051,9 @@
       <c r="J333" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K333" t="str">
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -11093,6 +12086,9 @@
       <c r="J334" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K334" t="str">
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -11125,6 +12121,9 @@
       <c r="J335" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K335" t="str">
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -11157,6 +12156,9 @@
       <c r="J336" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K336" t="str">
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -11189,6 +12191,9 @@
       <c r="J337" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K337" t="str">
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -11221,6 +12226,9 @@
       <c r="J338" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K338" t="str">
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -11253,6 +12261,9 @@
       <c r="J339" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K339" t="str">
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -11285,6 +12296,9 @@
       <c r="J340" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K340" t="str">
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -11317,6 +12331,9 @@
       <c r="J341" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K341" t="str">
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -11349,6 +12366,9 @@
       <c r="J342" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K342" t="str">
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -11381,6 +12401,9 @@
       <c r="J343" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K343" t="str">
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -11413,6 +12436,9 @@
       <c r="J344" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K344" t="str">
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -11445,6 +12471,9 @@
       <c r="J345" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K345" t="str">
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -11477,6 +12506,9 @@
       <c r="J346" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K346" t="str">
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -11509,6 +12541,9 @@
       <c r="J347" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K347" t="str">
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -11541,6 +12576,9 @@
       <c r="J348" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K348" t="str">
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -11573,6 +12611,9 @@
       <c r="J349" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K349" t="str">
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -11605,6 +12646,9 @@
       <c r="J350" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K350" t="str">
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -11637,6 +12681,9 @@
       <c r="J351" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K351" t="str">
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -11669,6 +12716,9 @@
       <c r="J352" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K352" t="str">
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -11701,6 +12751,9 @@
       <c r="J353" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K353" t="str">
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -11733,6 +12786,9 @@
       <c r="J354" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K354" t="str">
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -11765,6 +12821,9 @@
       <c r="J355" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K355" t="str">
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -11797,6 +12856,9 @@
       <c r="J356" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K356" t="str">
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -11829,6 +12891,9 @@
       <c r="J357" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K357" t="str">
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -11861,6 +12926,9 @@
       <c r="J358" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K358" t="str">
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -11893,6 +12961,9 @@
       <c r="J359" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K359" t="str">
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -11925,6 +12996,9 @@
       <c r="J360" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K360" t="str">
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -11957,6 +13031,9 @@
       <c r="J361" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K361" t="str">
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -11989,6 +13066,9 @@
       <c r="J362" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K362" t="str">
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -12021,6 +13101,9 @@
       <c r="J363" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K363" t="str">
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -12053,6 +13136,9 @@
       <c r="J364" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K364" t="str">
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -12085,6 +13171,9 @@
       <c r="J365" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K365" t="str">
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -12117,6 +13206,9 @@
       <c r="J366" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K366" t="str">
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -12149,6 +13241,9 @@
       <c r="J367" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K367" t="str">
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -12181,6 +13276,9 @@
       <c r="J368" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K368" t="str">
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -12213,6 +13311,9 @@
       <c r="J369" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K369" t="str">
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -12245,6 +13346,9 @@
       <c r="J370" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K370" t="str">
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -12277,6 +13381,9 @@
       <c r="J371" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K371" t="str">
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -12309,6 +13416,9 @@
       <c r="J372" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K372" t="str">
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -12341,6 +13451,9 @@
       <c r="J373" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K373" t="str">
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -12373,6 +13486,9 @@
       <c r="J374" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K374" t="str">
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -12405,6 +13521,9 @@
       <c r="J375" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K375" t="str">
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -12437,6 +13556,9 @@
       <c r="J376" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K376" t="str">
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -12469,6 +13591,9 @@
       <c r="J377" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K377" t="str">
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -12501,6 +13626,9 @@
       <c r="J378" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K378" t="str">
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -12533,6 +13661,9 @@
       <c r="J379" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K379" t="str">
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -12565,6 +13696,9 @@
       <c r="J380" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K380" t="str">
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -12597,6 +13731,9 @@
       <c r="J381" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K381" t="str">
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -12629,6 +13766,9 @@
       <c r="J382" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K382" t="str">
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -12661,6 +13801,9 @@
       <c r="J383" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K383" t="str">
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -12693,6 +13836,9 @@
       <c r="J384" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K384" t="str">
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -12725,6 +13871,9 @@
       <c r="J385" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K385" t="str">
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -12757,6 +13906,9 @@
       <c r="J386" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K386" t="str">
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -12789,6 +13941,9 @@
       <c r="J387" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K387" t="str">
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -12821,6 +13976,9 @@
       <c r="J388" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K388" t="str">
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -12853,6 +14011,9 @@
       <c r="J389" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K389" t="str">
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -12885,6 +14046,9 @@
       <c r="J390" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K390" t="str">
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
@@ -12917,6 +14081,9 @@
       <c r="J391" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K391" t="str">
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -12949,6 +14116,9 @@
       <c r="J392" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K392" t="str">
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -12981,6 +14151,9 @@
       <c r="J393" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K393" t="str">
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -13013,6 +14186,9 @@
       <c r="J394" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K394" t="str">
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -13045,6 +14221,9 @@
       <c r="J395" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K395" t="str">
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -13077,6 +14256,9 @@
       <c r="J396" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K396" t="str">
+        <v/>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
@@ -13109,6 +14291,9 @@
       <c r="J397" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K397" t="str">
+        <v/>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
@@ -13141,6 +14326,9 @@
       <c r="J398" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K398" t="str">
+        <v/>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
@@ -13173,6 +14361,9 @@
       <c r="J399" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K399" t="str">
+        <v/>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
@@ -13205,6 +14396,9 @@
       <c r="J400" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K400" t="str">
+        <v/>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
@@ -13237,6 +14431,9 @@
       <c r="J401" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K401" t="str">
+        <v/>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
@@ -13269,6 +14466,9 @@
       <c r="J402" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K402" t="str">
+        <v/>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
@@ -13301,6 +14501,9 @@
       <c r="J403" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K403" t="str">
+        <v/>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
@@ -13333,6 +14536,9 @@
       <c r="J404" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K404" t="str">
+        <v/>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
@@ -13365,6 +14571,9 @@
       <c r="J405" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K405" t="str">
+        <v/>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
@@ -13397,6 +14606,9 @@
       <c r="J406" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K406" t="str">
+        <v/>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
@@ -13429,6 +14641,9 @@
       <c r="J407" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K407" t="str">
+        <v/>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
@@ -13461,6 +14676,9 @@
       <c r="J408" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K408" t="str">
+        <v/>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
@@ -13493,6 +14711,9 @@
       <c r="J409" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K409" t="str">
+        <v/>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
@@ -13525,6 +14746,9 @@
       <c r="J410" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K410" t="str">
+        <v/>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
@@ -13557,6 +14781,9 @@
       <c r="J411" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K411" t="str">
+        <v/>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
@@ -13589,6 +14816,9 @@
       <c r="J412" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K412" t="str">
+        <v/>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
@@ -13621,6 +14851,9 @@
       <c r="J413" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K413" t="str">
+        <v/>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
@@ -13653,6 +14886,9 @@
       <c r="J414" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K414" t="str">
+        <v/>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
@@ -13685,6 +14921,9 @@
       <c r="J415" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K415" t="str">
+        <v/>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
@@ -13717,6 +14956,9 @@
       <c r="J416" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K416" t="str">
+        <v/>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
@@ -13749,6 +14991,9 @@
       <c r="J417" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K417" t="str">
+        <v/>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
@@ -13781,6 +15026,9 @@
       <c r="J418" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K418" t="str">
+        <v/>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
@@ -13813,6 +15061,9 @@
       <c r="J419" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K419" t="str">
+        <v/>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
@@ -13845,6 +15096,9 @@
       <c r="J420" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K420" t="str">
+        <v/>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
@@ -13877,6 +15131,9 @@
       <c r="J421" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K421" t="str">
+        <v/>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
@@ -13909,6 +15166,9 @@
       <c r="J422" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K422" t="str">
+        <v/>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
@@ -13941,6 +15201,9 @@
       <c r="J423" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K423" t="str">
+        <v/>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
@@ -13973,6 +15236,9 @@
       <c r="J424" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K424" t="str">
+        <v/>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
@@ -14005,6 +15271,9 @@
       <c r="J425" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K425" t="str">
+        <v/>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
@@ -14037,6 +15306,9 @@
       <c r="J426" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K426" t="str">
+        <v/>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
@@ -14069,6 +15341,9 @@
       <c r="J427" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K427" t="str">
+        <v/>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
@@ -14101,6 +15376,9 @@
       <c r="J428" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K428" t="str">
+        <v/>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
@@ -14133,6 +15411,9 @@
       <c r="J429" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K429" t="str">
+        <v/>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
@@ -14165,6 +15446,9 @@
       <c r="J430" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K430" t="str">
+        <v/>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
@@ -14197,6 +15481,9 @@
       <c r="J431" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K431" t="str">
+        <v/>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
@@ -14229,6 +15516,9 @@
       <c r="J432" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K432" t="str">
+        <v/>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
@@ -14261,6 +15551,9 @@
       <c r="J433" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K433" t="str">
+        <v/>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
@@ -14293,6 +15586,9 @@
       <c r="J434" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K434" t="str">
+        <v/>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
@@ -14325,6 +15621,9 @@
       <c r="J435" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K435" t="str">
+        <v/>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
@@ -14357,6 +15656,9 @@
       <c r="J436" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K436" t="str">
+        <v/>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
@@ -14389,6 +15691,9 @@
       <c r="J437" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K437" t="str">
+        <v/>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
@@ -14421,6 +15726,9 @@
       <c r="J438" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K438" t="str">
+        <v/>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
@@ -14453,6 +15761,9 @@
       <c r="J439" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K439" t="str">
+        <v/>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
@@ -14485,6 +15796,9 @@
       <c r="J440" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K440" t="str">
+        <v/>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
@@ -14517,6 +15831,9 @@
       <c r="J441" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K441" t="str">
+        <v/>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
@@ -14549,6 +15866,9 @@
       <c r="J442" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K442" t="str">
+        <v/>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
@@ -14581,6 +15901,9 @@
       <c r="J443" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K443" t="str">
+        <v/>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
@@ -14613,6 +15936,9 @@
       <c r="J444" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K444" t="str">
+        <v/>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
@@ -14645,6 +15971,9 @@
       <c r="J445" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K445" t="str">
+        <v/>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
@@ -14677,6 +16006,9 @@
       <c r="J446" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K446" t="str">
+        <v/>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
@@ -14709,6 +16041,9 @@
       <c r="J447" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K447" t="str">
+        <v/>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
@@ -14741,6 +16076,9 @@
       <c r="J448" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K448" t="str">
+        <v/>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
@@ -14773,6 +16111,9 @@
       <c r="J449" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K449" t="str">
+        <v/>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
@@ -14805,6 +16146,9 @@
       <c r="J450" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K450" t="str">
+        <v/>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
@@ -14837,6 +16181,9 @@
       <c r="J451" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K451" t="str">
+        <v/>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
@@ -14869,6 +16216,9 @@
       <c r="J452" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K452" t="str">
+        <v/>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
@@ -14901,6 +16251,9 @@
       <c r="J453" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K453" t="str">
+        <v/>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
@@ -14933,6 +16286,9 @@
       <c r="J454" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K454" t="str">
+        <v/>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
@@ -14965,6 +16321,9 @@
       <c r="J455" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K455" t="str">
+        <v/>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
@@ -14997,6 +16356,9 @@
       <c r="J456" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K456" t="str">
+        <v/>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
@@ -15029,6 +16391,9 @@
       <c r="J457" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K457" t="str">
+        <v/>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
@@ -15061,6 +16426,9 @@
       <c r="J458" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K458" t="str">
+        <v/>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
@@ -15093,6 +16461,9 @@
       <c r="J459" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K459" t="str">
+        <v/>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
@@ -15125,6 +16496,9 @@
       <c r="J460" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K460" t="str">
+        <v/>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
@@ -15157,6 +16531,9 @@
       <c r="J461" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K461" t="str">
+        <v/>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
@@ -15189,6 +16566,9 @@
       <c r="J462" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K462" t="str">
+        <v/>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
@@ -15221,6 +16601,9 @@
       <c r="J463" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K463" t="str">
+        <v/>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
@@ -15253,6 +16636,9 @@
       <c r="J464" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K464" t="str">
+        <v/>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
@@ -15285,6 +16671,9 @@
       <c r="J465" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K465" t="str">
+        <v/>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
@@ -15317,6 +16706,9 @@
       <c r="J466" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K466" t="str">
+        <v/>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
@@ -15349,6 +16741,9 @@
       <c r="J467" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K467" t="str">
+        <v/>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
@@ -15381,6 +16776,9 @@
       <c r="J468" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K468" t="str">
+        <v/>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
@@ -15413,6 +16811,9 @@
       <c r="J469" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K469" t="str">
+        <v/>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
@@ -15445,6 +16846,9 @@
       <c r="J470" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K470" t="str">
+        <v/>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
@@ -15477,6 +16881,9 @@
       <c r="J471" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K471" t="str">
+        <v/>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
@@ -15509,6 +16916,9 @@
       <c r="J472" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K472" t="str">
+        <v/>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
@@ -15541,6 +16951,9 @@
       <c r="J473" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K473" t="str">
+        <v/>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
@@ -15573,6 +16986,9 @@
       <c r="J474" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K474" t="str">
+        <v/>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
@@ -15605,6 +17021,9 @@
       <c r="J475" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K475" t="str">
+        <v/>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
@@ -15637,6 +17056,9 @@
       <c r="J476" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K476" t="str">
+        <v/>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
@@ -15669,6 +17091,9 @@
       <c r="J477" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K477" t="str">
+        <v/>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
@@ -15701,6 +17126,9 @@
       <c r="J478" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K478" t="str">
+        <v/>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
@@ -15733,6 +17161,9 @@
       <c r="J479" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K479" t="str">
+        <v/>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
@@ -15765,6 +17196,9 @@
       <c r="J480" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K480" t="str">
+        <v/>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
@@ -15797,6 +17231,9 @@
       <c r="J481" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K481" t="str">
+        <v/>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
@@ -15829,6 +17266,9 @@
       <c r="J482" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K482" t="str">
+        <v/>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
@@ -15861,6 +17301,9 @@
       <c r="J483" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K483" t="str">
+        <v/>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
@@ -15893,6 +17336,9 @@
       <c r="J484" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K484" t="str">
+        <v/>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
@@ -15925,6 +17371,9 @@
       <c r="J485" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K485" t="str">
+        <v/>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
@@ -15957,6 +17406,9 @@
       <c r="J486" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K486" t="str">
+        <v/>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
@@ -15989,6 +17441,9 @@
       <c r="J487" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K487" t="str">
+        <v/>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
@@ -16021,6 +17476,9 @@
       <c r="J488" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K488" t="str">
+        <v/>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
@@ -16053,6 +17511,9 @@
       <c r="J489" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K489" t="str">
+        <v/>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
@@ -16085,6 +17546,9 @@
       <c r="J490" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K490" t="str">
+        <v/>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
@@ -16117,6 +17581,9 @@
       <c r="J491" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K491" t="str">
+        <v/>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
@@ -16149,6 +17616,9 @@
       <c r="J492" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K492" t="str">
+        <v/>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
@@ -16181,6 +17651,9 @@
       <c r="J493" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K493" t="str">
+        <v/>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
@@ -16213,6 +17686,9 @@
       <c r="J494" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K494" t="str">
+        <v/>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
@@ -16245,6 +17721,9 @@
       <c r="J495" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K495" t="str">
+        <v/>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
@@ -16277,6 +17756,9 @@
       <c r="J496" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K496" t="str">
+        <v/>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
@@ -16309,6 +17791,9 @@
       <c r="J497" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K497" t="str">
+        <v/>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
@@ -16341,6 +17826,9 @@
       <c r="J498" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K498" t="str">
+        <v/>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
@@ -16373,6 +17861,9 @@
       <c r="J499" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K499" t="str">
+        <v/>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
@@ -16405,6 +17896,9 @@
       <c r="J500" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K500" t="str">
+        <v/>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
@@ -16437,6 +17931,9 @@
       <c r="J501" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K501" t="str">
+        <v/>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
@@ -16469,6 +17966,9 @@
       <c r="J502" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K502" t="str">
+        <v/>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
@@ -16501,6 +18001,9 @@
       <c r="J503" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K503" t="str">
+        <v/>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
@@ -16533,6 +18036,9 @@
       <c r="J504" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K504" t="str">
+        <v/>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
@@ -16565,6 +18071,9 @@
       <c r="J505" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K505" t="str">
+        <v/>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
@@ -16597,6 +18106,9 @@
       <c r="J506" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K506" t="str">
+        <v/>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
@@ -16629,6 +18141,9 @@
       <c r="J507" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K507" t="str">
+        <v/>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
@@ -16661,6 +18176,9 @@
       <c r="J508" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K508" t="str">
+        <v/>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
@@ -16693,6 +18211,9 @@
       <c r="J509" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K509" t="str">
+        <v/>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
@@ -16725,6 +18246,9 @@
       <c r="J510" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K510" t="str">
+        <v/>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
@@ -16757,6 +18281,9 @@
       <c r="J511" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K511" t="str">
+        <v/>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
@@ -16789,6 +18316,9 @@
       <c r="J512" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K512" t="str">
+        <v/>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
@@ -16821,6 +18351,9 @@
       <c r="J513" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K513" t="str">
+        <v/>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
@@ -16853,6 +18386,9 @@
       <c r="J514" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K514" t="str">
+        <v/>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
@@ -16885,6 +18421,9 @@
       <c r="J515" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K515" t="str">
+        <v/>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
@@ -16917,6 +18456,9 @@
       <c r="J516" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K516" t="str">
+        <v/>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
@@ -16949,6 +18491,9 @@
       <c r="J517" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K517" t="str">
+        <v/>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
@@ -16981,6 +18526,9 @@
       <c r="J518" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K518" t="str">
+        <v/>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
@@ -17013,6 +18561,9 @@
       <c r="J519" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K519" t="str">
+        <v/>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
@@ -17045,6 +18596,9 @@
       <c r="J520" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K520" t="str">
+        <v/>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
@@ -17077,6 +18631,9 @@
       <c r="J521" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K521" t="str">
+        <v/>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
@@ -17109,6 +18666,9 @@
       <c r="J522" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K522" t="str">
+        <v/>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
@@ -17141,6 +18701,9 @@
       <c r="J523" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K523" t="str">
+        <v/>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
@@ -17173,6 +18736,9 @@
       <c r="J524" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K524" t="str">
+        <v/>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
@@ -17205,6 +18771,9 @@
       <c r="J525" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K525" t="str">
+        <v/>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
@@ -17237,6 +18806,9 @@
       <c r="J526" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K526" t="str">
+        <v/>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
@@ -17269,6 +18841,9 @@
       <c r="J527" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K527" t="str">
+        <v/>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
@@ -17301,6 +18876,9 @@
       <c r="J528" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K528" t="str">
+        <v/>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
@@ -17333,6 +18911,9 @@
       <c r="J529" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K529" t="str">
+        <v/>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
@@ -17365,6 +18946,9 @@
       <c r="J530" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K530" t="str">
+        <v/>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
@@ -17397,6 +18981,9 @@
       <c r="J531" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K531" t="str">
+        <v/>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
@@ -17429,6 +19016,9 @@
       <c r="J532" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K532" t="str">
+        <v/>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
@@ -17461,6 +19051,9 @@
       <c r="J533" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K533" t="str">
+        <v/>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
@@ -17493,6 +19086,9 @@
       <c r="J534" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K534" t="str">
+        <v/>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
@@ -17525,6 +19121,9 @@
       <c r="J535" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K535" t="str">
+        <v/>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
@@ -17557,6 +19156,9 @@
       <c r="J536" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K536" t="str">
+        <v/>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
@@ -17589,6 +19191,9 @@
       <c r="J537" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K537" t="str">
+        <v/>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
@@ -17621,6 +19226,9 @@
       <c r="J538" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K538" t="str">
+        <v/>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
@@ -17653,6 +19261,9 @@
       <c r="J539" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K539" t="str">
+        <v/>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
@@ -17685,6 +19296,9 @@
       <c r="J540" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K540" t="str">
+        <v/>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
@@ -17717,6 +19331,9 @@
       <c r="J541" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K541" t="str">
+        <v/>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
@@ -17749,6 +19366,9 @@
       <c r="J542" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K542" t="str">
+        <v/>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
@@ -17781,6 +19401,9 @@
       <c r="J543" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K543" t="str">
+        <v/>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
@@ -17813,6 +19436,9 @@
       <c r="J544" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K544" t="str">
+        <v/>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
@@ -17845,6 +19471,9 @@
       <c r="J545" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K545" t="str">
+        <v/>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
@@ -17877,6 +19506,9 @@
       <c r="J546" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K546" t="str">
+        <v/>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
@@ -17909,6 +19541,9 @@
       <c r="J547" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K547" t="str">
+        <v/>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
@@ -17941,6 +19576,9 @@
       <c r="J548" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K548" t="str">
+        <v/>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
@@ -17973,6 +19611,9 @@
       <c r="J549" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K549" t="str">
+        <v/>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
@@ -18005,6 +19646,9 @@
       <c r="J550" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K550" t="str">
+        <v/>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
@@ -18037,6 +19681,9 @@
       <c r="J551" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K551" t="str">
+        <v/>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
@@ -18069,6 +19716,9 @@
       <c r="J552" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K552" t="str">
+        <v/>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
@@ -18101,6 +19751,9 @@
       <c r="J553" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K553" t="str">
+        <v/>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
@@ -18133,6 +19786,9 @@
       <c r="J554" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K554" t="str">
+        <v/>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
@@ -18165,6 +19821,9 @@
       <c r="J555" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K555" t="str">
+        <v/>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
@@ -18197,6 +19856,9 @@
       <c r="J556" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K556" t="str">
+        <v/>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
@@ -18229,6 +19891,9 @@
       <c r="J557" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K557" t="str">
+        <v/>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
@@ -18261,6 +19926,9 @@
       <c r="J558" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K558" t="str">
+        <v/>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
@@ -18293,6 +19961,9 @@
       <c r="J559" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K559" t="str">
+        <v/>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
@@ -18325,6 +19996,9 @@
       <c r="J560" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K560" t="str">
+        <v/>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
@@ -18357,6 +20031,9 @@
       <c r="J561" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K561" t="str">
+        <v/>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
@@ -18389,6 +20066,9 @@
       <c r="J562" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K562" t="str">
+        <v/>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
@@ -18421,6 +20101,9 @@
       <c r="J563" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K563" t="str">
+        <v/>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
@@ -18453,6 +20136,9 @@
       <c r="J564" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K564" t="str">
+        <v/>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
@@ -18485,6 +20171,9 @@
       <c r="J565" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K565" t="str">
+        <v/>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
@@ -18517,6 +20206,9 @@
       <c r="J566" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K566" t="str">
+        <v/>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
@@ -18549,6 +20241,9 @@
       <c r="J567" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K567" t="str">
+        <v/>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
@@ -18581,6 +20276,9 @@
       <c r="J568" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K568" t="str">
+        <v/>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
@@ -18613,6 +20311,9 @@
       <c r="J569" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K569" t="str">
+        <v/>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
@@ -18645,6 +20346,9 @@
       <c r="J570" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K570" t="str">
+        <v/>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
@@ -18677,6 +20381,9 @@
       <c r="J571" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K571" t="str">
+        <v/>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
@@ -18709,6 +20416,9 @@
       <c r="J572" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K572" t="str">
+        <v/>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
@@ -18741,6 +20451,9 @@
       <c r="J573" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K573" t="str">
+        <v/>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
@@ -18773,6 +20486,9 @@
       <c r="J574" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K574" t="str">
+        <v/>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
@@ -18805,6 +20521,9 @@
       <c r="J575" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K575" t="str">
+        <v/>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
@@ -18837,6 +20556,9 @@
       <c r="J576" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K576" t="str">
+        <v/>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
@@ -18869,6 +20591,9 @@
       <c r="J577" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K577" t="str">
+        <v/>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
@@ -18901,6 +20626,9 @@
       <c r="J578" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K578" t="str">
+        <v/>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
@@ -18933,6 +20661,9 @@
       <c r="J579" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K579" t="str">
+        <v/>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
@@ -18965,6 +20696,9 @@
       <c r="J580" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K580" t="str">
+        <v/>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
@@ -18997,6 +20731,9 @@
       <c r="J581" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K581" t="str">
+        <v/>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
@@ -19029,6 +20766,9 @@
       <c r="J582" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K582" t="str">
+        <v/>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
@@ -19061,6 +20801,9 @@
       <c r="J583" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K583" t="str">
+        <v/>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
@@ -19093,6 +20836,9 @@
       <c r="J584" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K584" t="str">
+        <v/>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
@@ -19125,6 +20871,9 @@
       <c r="J585" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K585" t="str">
+        <v/>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
@@ -19157,6 +20906,9 @@
       <c r="J586" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K586" t="str">
+        <v/>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
@@ -19189,6 +20941,9 @@
       <c r="J587" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K587" t="str">
+        <v/>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
@@ -19221,6 +20976,9 @@
       <c r="J588" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K588" t="str">
+        <v/>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
@@ -19253,6 +21011,9 @@
       <c r="J589" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K589" t="str">
+        <v/>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
@@ -19285,6 +21046,9 @@
       <c r="J590" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K590" t="str">
+        <v/>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
@@ -19317,6 +21081,9 @@
       <c r="J591" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K591" t="str">
+        <v/>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
@@ -19349,6 +21116,9 @@
       <c r="J592" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K592" t="str">
+        <v/>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
@@ -19381,6 +21151,9 @@
       <c r="J593" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K593" t="str">
+        <v/>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
@@ -19413,6 +21186,9 @@
       <c r="J594" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K594" t="str">
+        <v/>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
@@ -19445,6 +21221,9 @@
       <c r="J595" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K595" t="str">
+        <v/>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
@@ -19477,6 +21256,9 @@
       <c r="J596" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K596" t="str">
+        <v/>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
@@ -19509,6 +21291,9 @@
       <c r="J597" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K597" t="str">
+        <v/>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
@@ -19541,6 +21326,9 @@
       <c r="J598" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K598" t="str">
+        <v/>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
@@ -19573,6 +21361,9 @@
       <c r="J599" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K599" t="str">
+        <v/>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
@@ -19605,6 +21396,9 @@
       <c r="J600" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K600" t="str">
+        <v/>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
@@ -19637,6 +21431,9 @@
       <c r="J601" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K601" t="str">
+        <v/>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
@@ -19669,6 +21466,9 @@
       <c r="J602" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K602" t="str">
+        <v/>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
@@ -19701,6 +21501,9 @@
       <c r="J603" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K603" t="str">
+        <v/>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
@@ -19733,6 +21536,9 @@
       <c r="J604" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K604" t="str">
+        <v/>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
@@ -19765,6 +21571,9 @@
       <c r="J605" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K605" t="str">
+        <v/>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
@@ -19797,6 +21606,9 @@
       <c r="J606" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K606" t="str">
+        <v/>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
@@ -19829,6 +21641,9 @@
       <c r="J607" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K607" t="str">
+        <v/>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
@@ -19861,6 +21676,9 @@
       <c r="J608" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K608" t="str">
+        <v/>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
@@ -19893,6 +21711,9 @@
       <c r="J609" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K609" t="str">
+        <v/>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
@@ -19925,6 +21746,9 @@
       <c r="J610" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K610" t="str">
+        <v/>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
@@ -19957,6 +21781,9 @@
       <c r="J611" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K611" t="str">
+        <v/>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
@@ -19989,6 +21816,9 @@
       <c r="J612" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K612" t="str">
+        <v/>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
@@ -20021,6 +21851,9 @@
       <c r="J613" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K613" t="str">
+        <v/>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
@@ -20053,6 +21886,9 @@
       <c r="J614" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K614" t="str">
+        <v/>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
@@ -20085,6 +21921,9 @@
       <c r="J615" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K615" t="str">
+        <v/>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
@@ -20117,6 +21956,9 @@
       <c r="J616" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K616" t="str">
+        <v/>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
@@ -20149,6 +21991,9 @@
       <c r="J617" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K617" t="str">
+        <v/>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
@@ -20181,6 +22026,9 @@
       <c r="J618" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K618" t="str">
+        <v/>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
@@ -20213,6 +22061,9 @@
       <c r="J619" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K619" t="str">
+        <v/>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
@@ -20245,6 +22096,9 @@
       <c r="J620" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K620" t="str">
+        <v/>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
@@ -20277,6 +22131,9 @@
       <c r="J621" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K621" t="str">
+        <v/>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
@@ -20309,6 +22166,9 @@
       <c r="J622" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K622" t="str">
+        <v/>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
@@ -20341,6 +22201,9 @@
       <c r="J623" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K623" t="str">
+        <v/>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
@@ -20373,6 +22236,9 @@
       <c r="J624" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K624" t="str">
+        <v/>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
@@ -20405,6 +22271,9 @@
       <c r="J625" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K625" t="str">
+        <v/>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
@@ -20437,6 +22306,9 @@
       <c r="J626" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K626" t="str">
+        <v/>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
@@ -20469,6 +22341,9 @@
       <c r="J627" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K627" t="str">
+        <v/>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
@@ -20501,6 +22376,9 @@
       <c r="J628" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K628" t="str">
+        <v/>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
@@ -20533,6 +22411,9 @@
       <c r="J629" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K629" t="str">
+        <v/>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
@@ -20565,6 +22446,9 @@
       <c r="J630" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K630" t="str">
+        <v/>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
@@ -20597,6 +22481,9 @@
       <c r="J631" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K631" t="str">
+        <v/>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
@@ -20629,6 +22516,9 @@
       <c r="J632" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K632" t="str">
+        <v/>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
@@ -20661,6 +22551,9 @@
       <c r="J633" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K633" t="str">
+        <v/>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
@@ -20693,6 +22586,9 @@
       <c r="J634" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K634" t="str">
+        <v/>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
@@ -20725,6 +22621,9 @@
       <c r="J635" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K635" t="str">
+        <v/>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
@@ -20757,6 +22656,9 @@
       <c r="J636" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K636" t="str">
+        <v/>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
@@ -20789,6 +22691,9 @@
       <c r="J637" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K637" t="str">
+        <v/>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
@@ -20821,6 +22726,9 @@
       <c r="J638" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K638" t="str">
+        <v/>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
@@ -20853,6 +22761,9 @@
       <c r="J639" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K639" t="str">
+        <v/>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
@@ -20885,6 +22796,9 @@
       <c r="J640" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K640" t="str">
+        <v/>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
@@ -20917,6 +22831,9 @@
       <c r="J641" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K641" t="str">
+        <v/>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
@@ -20949,6 +22866,9 @@
       <c r="J642" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K642" t="str">
+        <v/>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
@@ -20981,6 +22901,9 @@
       <c r="J643" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K643" t="str">
+        <v/>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
@@ -21013,6 +22936,9 @@
       <c r="J644" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K644" t="str">
+        <v/>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
@@ -21045,6 +22971,9 @@
       <c r="J645" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K645" t="str">
+        <v/>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
@@ -21077,6 +23006,9 @@
       <c r="J646" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K646" t="str">
+        <v/>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
@@ -21109,6 +23041,9 @@
       <c r="J647" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K647" t="str">
+        <v/>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
@@ -21141,6 +23076,9 @@
       <c r="J648" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K648" t="str">
+        <v/>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
@@ -21173,6 +23111,9 @@
       <c r="J649" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K649" t="str">
+        <v/>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
@@ -21205,6 +23146,9 @@
       <c r="J650" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K650" t="str">
+        <v/>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
@@ -21237,6 +23181,9 @@
       <c r="J651" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K651" t="str">
+        <v/>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
@@ -21269,6 +23216,9 @@
       <c r="J652" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K652" t="str">
+        <v/>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
@@ -21301,6 +23251,9 @@
       <c r="J653" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K653" t="str">
+        <v/>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
@@ -21333,6 +23286,9 @@
       <c r="J654" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K654" t="str">
+        <v/>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
@@ -21365,6 +23321,9 @@
       <c r="J655" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K655" t="str">
+        <v/>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
@@ -21397,6 +23356,9 @@
       <c r="J656" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K656" t="str">
+        <v/>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
@@ -21429,6 +23391,9 @@
       <c r="J657" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K657" t="str">
+        <v/>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
@@ -21461,6 +23426,9 @@
       <c r="J658" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K658" t="str">
+        <v/>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
@@ -21493,6 +23461,9 @@
       <c r="J659" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K659" t="str">
+        <v/>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
@@ -21525,6 +23496,9 @@
       <c r="J660" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K660" t="str">
+        <v/>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
@@ -21557,6 +23531,9 @@
       <c r="J661" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K661" t="str">
+        <v/>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
@@ -21589,6 +23566,9 @@
       <c r="J662" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K662" t="str">
+        <v/>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
@@ -21621,6 +23601,9 @@
       <c r="J663" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K663" t="str">
+        <v/>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
@@ -21653,6 +23636,9 @@
       <c r="J664" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K664" t="str">
+        <v/>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
@@ -21685,6 +23671,9 @@
       <c r="J665" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K665" t="str">
+        <v/>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
@@ -21717,6 +23706,9 @@
       <c r="J666" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K666" t="str">
+        <v/>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
@@ -21749,6 +23741,9 @@
       <c r="J667" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K667" t="str">
+        <v/>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
@@ -21781,6 +23776,9 @@
       <c r="J668" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K668" t="str">
+        <v/>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
@@ -21813,6 +23811,9 @@
       <c r="J669" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K669" t="str">
+        <v/>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
@@ -21845,6 +23846,9 @@
       <c r="J670" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K670" t="str">
+        <v/>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
@@ -21877,6 +23881,9 @@
       <c r="J671" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K671" t="str">
+        <v/>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
@@ -21909,6 +23916,9 @@
       <c r="J672" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K672" t="str">
+        <v/>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
@@ -21941,6 +23951,9 @@
       <c r="J673" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K673" t="str">
+        <v/>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
@@ -21973,6 +23986,9 @@
       <c r="J674" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K674" t="str">
+        <v/>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
@@ -22005,6 +24021,9 @@
       <c r="J675" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K675" t="str">
+        <v/>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
@@ -22037,6 +24056,9 @@
       <c r="J676" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K676" t="str">
+        <v/>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
@@ -22069,6 +24091,9 @@
       <c r="J677" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K677" t="str">
+        <v/>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
@@ -22101,6 +24126,9 @@
       <c r="J678" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K678" t="str">
+        <v/>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
@@ -22133,6 +24161,9 @@
       <c r="J679" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K679" t="str">
+        <v/>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
@@ -22165,6 +24196,9 @@
       <c r="J680" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K680" t="str">
+        <v/>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
@@ -22197,6 +24231,9 @@
       <c r="J681" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K681" t="str">
+        <v/>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
@@ -22229,6 +24266,9 @@
       <c r="J682" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K682" t="str">
+        <v/>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
@@ -22261,6 +24301,9 @@
       <c r="J683" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K683" t="str">
+        <v/>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
@@ -22293,6 +24336,9 @@
       <c r="J684" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K684" t="str">
+        <v/>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
@@ -22325,6 +24371,9 @@
       <c r="J685" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K685" t="str">
+        <v/>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
@@ -22357,6 +24406,9 @@
       <c r="J686" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K686" t="str">
+        <v/>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
@@ -22389,6 +24441,9 @@
       <c r="J687" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K687" t="str">
+        <v/>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
@@ -22421,6 +24476,9 @@
       <c r="J688" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K688" t="str">
+        <v/>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
@@ -22453,6 +24511,9 @@
       <c r="J689" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K689" t="str">
+        <v/>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
@@ -22485,6 +24546,9 @@
       <c r="J690" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K690" t="str">
+        <v/>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
@@ -22517,6 +24581,9 @@
       <c r="J691" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K691" t="str">
+        <v/>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
@@ -22549,6 +24616,9 @@
       <c r="J692" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K692" t="str">
+        <v/>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
@@ -22581,6 +24651,9 @@
       <c r="J693" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K693" t="str">
+        <v/>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
@@ -22613,6 +24686,9 @@
       <c r="J694" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K694" t="str">
+        <v/>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
@@ -22645,6 +24721,9 @@
       <c r="J695" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K695" t="str">
+        <v/>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
@@ -22677,6 +24756,9 @@
       <c r="J696" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K696" t="str">
+        <v/>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
@@ -22709,6 +24791,9 @@
       <c r="J697" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K697" t="str">
+        <v/>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
@@ -22741,6 +24826,9 @@
       <c r="J698" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K698" t="str">
+        <v/>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
@@ -22773,6 +24861,9 @@
       <c r="J699" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K699" t="str">
+        <v/>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
@@ -22805,6 +24896,9 @@
       <c r="J700" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K700" t="str">
+        <v/>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
@@ -22837,6 +24931,9 @@
       <c r="J701" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K701" t="str">
+        <v/>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
@@ -22869,6 +24966,9 @@
       <c r="J702" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K702" t="str">
+        <v/>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
@@ -22901,6 +25001,9 @@
       <c r="J703" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K703" t="str">
+        <v/>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
@@ -22933,6 +25036,9 @@
       <c r="J704" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K704" t="str">
+        <v/>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
@@ -22965,6 +25071,9 @@
       <c r="J705" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K705" t="str">
+        <v/>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
@@ -22997,6 +25106,9 @@
       <c r="J706" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K706" t="str">
+        <v/>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
@@ -23029,6 +25141,9 @@
       <c r="J707" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K707" t="str">
+        <v/>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
@@ -23061,6 +25176,9 @@
       <c r="J708" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K708" t="str">
+        <v/>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
@@ -23093,6 +25211,9 @@
       <c r="J709" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K709" t="str">
+        <v/>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
@@ -23125,6 +25246,9 @@
       <c r="J710" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K710" t="str">
+        <v/>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
@@ -23157,6 +25281,9 @@
       <c r="J711" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K711" t="str">
+        <v/>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
@@ -23189,6 +25316,9 @@
       <c r="J712" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K712" t="str">
+        <v/>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
@@ -23221,6 +25351,9 @@
       <c r="J713" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K713" t="str">
+        <v/>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
@@ -23253,6 +25386,9 @@
       <c r="J714" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K714" t="str">
+        <v/>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
@@ -23285,6 +25421,9 @@
       <c r="J715" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K715" t="str">
+        <v/>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
@@ -23317,6 +25456,9 @@
       <c r="J716" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K716" t="str">
+        <v/>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
@@ -23349,6 +25491,9 @@
       <c r="J717" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K717" t="str">
+        <v/>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
@@ -23381,6 +25526,9 @@
       <c r="J718" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K718" t="str">
+        <v/>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
@@ -23413,6 +25561,9 @@
       <c r="J719" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K719" t="str">
+        <v/>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
@@ -23445,6 +25596,9 @@
       <c r="J720" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K720" t="str">
+        <v/>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
@@ -23477,6 +25631,9 @@
       <c r="J721" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K721" t="str">
+        <v/>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
@@ -23509,6 +25666,9 @@
       <c r="J722" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K722" t="str">
+        <v/>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
@@ -23541,6 +25701,9 @@
       <c r="J723" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K723" t="str">
+        <v/>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
@@ -23573,6 +25736,9 @@
       <c r="J724" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K724" t="str">
+        <v/>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
@@ -23605,6 +25771,9 @@
       <c r="J725" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K725" t="str">
+        <v/>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
@@ -23637,6 +25806,9 @@
       <c r="J726" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K726" t="str">
+        <v/>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
@@ -23669,6 +25841,9 @@
       <c r="J727" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K727" t="str">
+        <v/>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
@@ -23701,6 +25876,9 @@
       <c r="J728" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K728" t="str">
+        <v/>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
@@ -23733,6 +25911,9 @@
       <c r="J729" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K729" t="str">
+        <v/>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
@@ -23763,6 +25944,9 @@
         <v/>
       </c>
       <c r="J730" t="str">
+        <v/>
+      </c>
+      <c r="K730" t="str">
         <v/>
       </c>
     </row>

--- a/ERDEMLİ.xlsx
+++ b/ERDEMLİ.xlsx
@@ -913,16 +913,16 @@
         <v>Yol</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>Kısmen yoldan kısmen Parktan ihdas</v>
       </c>
       <c r="J15" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="16">

--- a/ERDEMLİ.xlsx
+++ b/ERDEMLİ.xlsx
@@ -1893,16 +1893,16 @@
         <v>Park</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>ARSA-152 ada 15 parselden parka terk edilen alan</v>
       </c>
       <c r="J43" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
       <c r="K43" t="str">
-        <v/>
+        <v>2026-04-09</v>
       </c>
     </row>
     <row r="44">
